--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,30 +434,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dropout</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Weight_Decay</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Epochs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Macro_F1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Weighted_F1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Training_Time</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Memory_MB</t>
         </is>
@@ -480,22 +505,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8110000000000001</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8027</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8123</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>0.0005</v>
       </c>
       <c r="H2" t="n">
-        <v>46119</v>
+        <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>361.03</v>
+        <v>0.749</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7472</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7484</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="N2" t="n">
+        <v>373.66</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +555,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.784</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>0.78</v>
+        <v>0.01</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7879</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.21</v>
+        <v>0.0005</v>
       </c>
       <c r="H3" t="n">
-        <v>369429</v>
+        <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>459.03</v>
+        <v>0.779</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7711</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7799</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>369941</v>
+      </c>
+      <c r="N3" t="n">
+        <v>473.14</v>
       </c>
     </row>
     <row r="4">
@@ -550,22 +605,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.803</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>0.791</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8042</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.26</v>
+        <v>0.0005</v>
       </c>
       <c r="H4" t="n">
-        <v>92199</v>
+        <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>458.74</v>
+        <v>0.773</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>92263</v>
+      </c>
+      <c r="N4" t="n">
+        <v>471.27</v>
       </c>
     </row>
     <row r="5">
@@ -585,22 +655,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.757</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7558</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7561</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>48231</v>
+        <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>441.26</v>
+        <v>0.755</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7556</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M5" t="n">
+        <v>47239</v>
+      </c>
+      <c r="N5" t="n">
+        <v>454.39</v>
       </c>
     </row>
     <row r="6">
@@ -620,22 +705,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6850000000000001</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6595</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6915</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.39</v>
+        <v>0.0005</v>
       </c>
       <c r="H6" t="n">
-        <v>118726</v>
+        <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>394.55</v>
+        <v>0.606</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6177</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>118790</v>
+      </c>
+      <c r="N6" t="n">
+        <v>407.03</v>
       </c>
     </row>
     <row r="7">
@@ -655,22 +755,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.634</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6166</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6475</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.15</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>950290</v>
+        <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>484.59</v>
+        <v>0.66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6609</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>950802</v>
+      </c>
+      <c r="N7" t="n">
+        <v>504.15</v>
       </c>
     </row>
     <row r="8">
@@ -690,22 +805,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.701</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6684</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7017</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>7.79</v>
+        <v>0.0005</v>
       </c>
       <c r="H8" t="n">
-        <v>237414</v>
+        <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>630.4299999999999</v>
+        <v>0.641</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M8" t="n">
+        <v>237478</v>
+      </c>
+      <c r="N8" t="n">
+        <v>642.12</v>
       </c>
     </row>
     <row r="9">
@@ -725,22 +855,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.631</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6047</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>0.639</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.95</v>
+        <v>0.0005</v>
       </c>
       <c r="H9" t="n">
-        <v>120838</v>
+        <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>579.04</v>
+        <v>0.511</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="M9" t="n">
+        <v>119846</v>
+      </c>
+      <c r="N9" t="n">
+        <v>591.48</v>
       </c>
     </row>
     <row r="10">
@@ -760,22 +905,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.792</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7882</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7917</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8</v>
+        <v>0.0005</v>
       </c>
       <c r="H10" t="n">
-        <v>16131</v>
+        <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>437.39</v>
+        <v>0.733</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7271</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16195</v>
+      </c>
+      <c r="N10" t="n">
+        <v>453.06</v>
       </c>
     </row>
     <row r="11">
@@ -795,22 +955,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.763</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7631</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>26.64</v>
+        <v>0.0005</v>
       </c>
       <c r="H11" t="n">
-        <v>129545</v>
+        <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>947.89</v>
+        <v>0.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7504</v>
+      </c>
+      <c r="L11" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>130057</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1012.89</v>
       </c>
     </row>
     <row r="12">
@@ -830,22 +1005,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.766</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7615</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>0.766</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>8.26</v>
+        <v>0.0005</v>
       </c>
       <c r="H12" t="n">
-        <v>32227</v>
+        <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>641.14</v>
+        <v>0.742</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7422</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>32291</v>
+      </c>
+      <c r="N12" t="n">
+        <v>672</v>
       </c>
     </row>
     <row r="13">
@@ -865,22 +1055,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.76</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>0.753</v>
+        <v>0.01</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7603</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>8.4</v>
+        <v>0.0005</v>
       </c>
       <c r="H13" t="n">
-        <v>18243</v>
+        <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>596.79</v>
+        <v>0.745</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7321</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7451</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17251</v>
+      </c>
+      <c r="N13" t="n">
+        <v>631.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -520,22 +520,22 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.749</v>
+        <v>0.73</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7472</v>
+        <v>0.7291</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7484</v>
+        <v>0.7309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.73</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
-        <v>46183</v>
+        <v>47239</v>
       </c>
       <c r="N2" t="n">
-        <v>373.66</v>
+        <v>373.62</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>0.7799</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
         <v>369941</v>
       </c>
       <c r="N3" t="n">
-        <v>473.14</v>
+        <v>475.01</v>
       </c>
     </row>
     <row r="4">
@@ -629,13 +629,13 @@
         <v>0.7742</v>
       </c>
       <c r="L4" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="M4" t="n">
         <v>92263</v>
       </c>
       <c r="N4" t="n">
-        <v>471.27</v>
+        <v>469.68</v>
       </c>
     </row>
     <row r="5">
@@ -679,13 +679,13 @@
         <v>0.7556</v>
       </c>
       <c r="L5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
         <v>47239</v>
       </c>
       <c r="N5" t="n">
-        <v>454.39</v>
+        <v>452.86</v>
       </c>
     </row>
     <row r="6">
@@ -720,22 +720,22 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.606</v>
+        <v>0.597</v>
       </c>
       <c r="J6" t="n">
-        <v>0.584</v>
+        <v>0.576</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6177</v>
+        <v>0.6047</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>118790</v>
+        <v>119846</v>
       </c>
       <c r="N6" t="n">
-        <v>407.03</v>
+        <v>408.96</v>
       </c>
     </row>
     <row r="7">
@@ -785,7 +785,7 @@
         <v>950802</v>
       </c>
       <c r="N7" t="n">
-        <v>504.15</v>
+        <v>505.91</v>
       </c>
     </row>
     <row r="8">
@@ -829,13 +829,13 @@
         <v>0.6515</v>
       </c>
       <c r="L8" t="n">
-        <v>8.74</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>237478</v>
       </c>
       <c r="N8" t="n">
-        <v>642.12</v>
+        <v>642.02</v>
       </c>
     </row>
     <row r="9">
@@ -879,13 +879,13 @@
         <v>0.519</v>
       </c>
       <c r="L9" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="M9" t="n">
         <v>119846</v>
       </c>
       <c r="N9" t="n">
-        <v>591.48</v>
+        <v>591.21</v>
       </c>
     </row>
     <row r="10">
@@ -920,22 +920,22 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.733</v>
+        <v>0.72</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7271</v>
+        <v>0.7133</v>
       </c>
       <c r="K10" t="n">
-        <v>0.734</v>
+        <v>0.7202</v>
       </c>
       <c r="L10" t="n">
-        <v>2.69</v>
+        <v>4.72</v>
       </c>
       <c r="M10" t="n">
-        <v>16195</v>
+        <v>17251</v>
       </c>
       <c r="N10" t="n">
-        <v>453.06</v>
+        <v>468.32</v>
       </c>
     </row>
     <row r="11">
@@ -979,13 +979,13 @@
         <v>0.7504</v>
       </c>
       <c r="L11" t="n">
-        <v>14.11</v>
+        <v>13.93</v>
       </c>
       <c r="M11" t="n">
         <v>130057</v>
       </c>
       <c r="N11" t="n">
-        <v>1012.89</v>
+        <v>1013.92</v>
       </c>
     </row>
     <row r="12">
@@ -1029,13 +1029,13 @@
         <v>0.7422</v>
       </c>
       <c r="L12" t="n">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="M12" t="n">
         <v>32291</v>
       </c>
       <c r="N12" t="n">
-        <v>672</v>
+        <v>671.08</v>
       </c>
     </row>
     <row r="13">
@@ -1085,7 +1085,7 @@
         <v>17251</v>
       </c>
       <c r="N13" t="n">
-        <v>631.2</v>
+        <v>630.1900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -520,22 +520,22 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7291</v>
+        <v>0.745</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7309</v>
+        <v>0.7516</v>
       </c>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
       <c r="M2" t="n">
         <v>47239</v>
       </c>
       <c r="N2" t="n">
-        <v>373.62</v>
+        <v>374.67</v>
       </c>
     </row>
     <row r="3">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -529,13 +529,13 @@
         <v>0.7516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="M2" t="n">
         <v>47239</v>
       </c>
       <c r="N2" t="n">
-        <v>374.67</v>
+        <v>373.76</v>
       </c>
     </row>
     <row r="3">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -529,13 +529,13 @@
         <v>0.7516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="M2" t="n">
         <v>47239</v>
       </c>
       <c r="N2" t="n">
-        <v>373.76</v>
+        <v>374.39</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>0.7799</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="M3" t="n">
         <v>369941</v>
       </c>
       <c r="N3" t="n">
-        <v>475.01</v>
+        <v>474.97</v>
       </c>
     </row>
     <row r="4">
@@ -629,13 +629,13 @@
         <v>0.7742</v>
       </c>
       <c r="L4" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="M4" t="n">
         <v>92263</v>
       </c>
       <c r="N4" t="n">
-        <v>469.68</v>
+        <v>471.17</v>
       </c>
     </row>
     <row r="5">
@@ -679,13 +679,13 @@
         <v>0.7556</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="M5" t="n">
         <v>47239</v>
       </c>
       <c r="N5" t="n">
-        <v>452.86</v>
+        <v>453.87</v>
       </c>
     </row>
     <row r="6">
@@ -720,22 +720,22 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.597</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.576</v>
+        <v>0.5404</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6047</v>
+        <v>0.5634</v>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>119846</v>
       </c>
       <c r="N6" t="n">
-        <v>408.96</v>
+        <v>408.3</v>
       </c>
     </row>
     <row r="7">
@@ -779,13 +779,13 @@
         <v>0.6609</v>
       </c>
       <c r="L7" t="n">
-        <v>3.01</v>
+        <v>4.66</v>
       </c>
       <c r="M7" t="n">
         <v>950802</v>
       </c>
       <c r="N7" t="n">
-        <v>505.91</v>
+        <v>503.75</v>
       </c>
     </row>
     <row r="8">
@@ -829,13 +829,13 @@
         <v>0.6515</v>
       </c>
       <c r="L8" t="n">
-        <v>8.619999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="M8" t="n">
         <v>237478</v>
       </c>
       <c r="N8" t="n">
-        <v>642.02</v>
+        <v>634.77</v>
       </c>
     </row>
     <row r="9">
@@ -879,13 +879,13 @@
         <v>0.519</v>
       </c>
       <c r="L9" t="n">
-        <v>3.81</v>
+        <v>4.57</v>
       </c>
       <c r="M9" t="n">
         <v>119846</v>
       </c>
       <c r="N9" t="n">
-        <v>591.21</v>
+        <v>591.66</v>
       </c>
     </row>
     <row r="10">
@@ -920,22 +920,22 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.72</v>
+        <v>0.751</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7133</v>
+        <v>0.7443</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7202</v>
+        <v>0.751</v>
       </c>
       <c r="L10" t="n">
-        <v>4.72</v>
+        <v>3.68</v>
       </c>
       <c r="M10" t="n">
         <v>17251</v>
       </c>
       <c r="N10" t="n">
-        <v>468.32</v>
+        <v>463.08</v>
       </c>
     </row>
     <row r="11">
@@ -979,13 +979,13 @@
         <v>0.7504</v>
       </c>
       <c r="L11" t="n">
-        <v>13.93</v>
+        <v>17.26</v>
       </c>
       <c r="M11" t="n">
         <v>130057</v>
       </c>
       <c r="N11" t="n">
-        <v>1013.92</v>
+        <v>1013.52</v>
       </c>
     </row>
     <row r="12">
@@ -1029,13 +1029,13 @@
         <v>0.7422</v>
       </c>
       <c r="L12" t="n">
-        <v>6.27</v>
+        <v>7.57</v>
       </c>
       <c r="M12" t="n">
         <v>32291</v>
       </c>
       <c r="N12" t="n">
-        <v>671.08</v>
+        <v>671.6900000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1079,13 +1079,13 @@
         <v>0.7451</v>
       </c>
       <c r="L13" t="n">
-        <v>4.58</v>
+        <v>5.48</v>
       </c>
       <c r="M13" t="n">
         <v>17251</v>
       </c>
       <c r="N13" t="n">
-        <v>630.1900000000001</v>
+        <v>631.6900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -520,22 +520,22 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.745</v>
+        <v>0.6912</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7516</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>47239</v>
+        <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>374.39</v>
+        <v>375.18</v>
       </c>
     </row>
     <row r="3">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -529,13 +529,13 @@
         <v>0.7050999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>375.18</v>
+        <v>374.24</v>
       </c>
     </row>
     <row r="3">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -529,13 +529,13 @@
         <v>0.7050999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="M2" t="n">
         <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>374.24</v>
+        <v>392.57</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.779</v>
+        <v>0.759</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7711</v>
+        <v>0.7552</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7799</v>
+        <v>0.7628</v>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>5.28</v>
       </c>
       <c r="M3" t="n">
-        <v>369941</v>
+        <v>370011</v>
       </c>
       <c r="N3" t="n">
-        <v>474.97</v>
+        <v>467.67</v>
       </c>
     </row>
     <row r="4">
@@ -620,22 +620,22 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.773</v>
+        <v>0.667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7647</v>
+        <v>0.6565</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7742</v>
+        <v>0.6639</v>
       </c>
       <c r="L4" t="n">
-        <v>2.73</v>
+        <v>5.45</v>
       </c>
       <c r="M4" t="n">
-        <v>92263</v>
+        <v>92333</v>
       </c>
       <c r="N4" t="n">
-        <v>471.17</v>
+        <v>476.83</v>
       </c>
     </row>
     <row r="5">
@@ -670,22 +670,22 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.755</v>
+        <v>0.548</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7496</v>
+        <v>0.5774</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7556</v>
+        <v>0.5356</v>
       </c>
       <c r="L5" t="n">
-        <v>2.62</v>
+        <v>4.61</v>
       </c>
       <c r="M5" t="n">
-        <v>47239</v>
+        <v>47309</v>
       </c>
       <c r="N5" t="n">
-        <v>453.87</v>
+        <v>459.49</v>
       </c>
     </row>
     <row r="6">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -520,22 +520,22 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7</v>
+        <v>0.676</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6912</v>
+        <v>0.6765</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6735</v>
       </c>
       <c r="L2" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="M2" t="n">
         <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>392.57</v>
+        <v>387.28</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.759</v>
+        <v>0.719</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7552</v>
+        <v>0.7096</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7628</v>
+        <v>0.7215</v>
       </c>
       <c r="L3" t="n">
-        <v>5.28</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>370011</v>
+        <v>47431</v>
       </c>
       <c r="N3" t="n">
-        <v>467.67</v>
+        <v>399.02</v>
       </c>
     </row>
     <row r="4">
@@ -620,22 +620,22 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.667</v>
+        <v>0.729</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6565</v>
+        <v>0.7188</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6639</v>
+        <v>0.731</v>
       </c>
       <c r="L4" t="n">
-        <v>5.45</v>
+        <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>92333</v>
+        <v>94183</v>
       </c>
       <c r="N4" t="n">
-        <v>476.83</v>
+        <v>482.79</v>
       </c>
     </row>
     <row r="5">
@@ -670,22 +670,22 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.548</v>
+        <v>0.587</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5774</v>
+        <v>0.5995</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5356</v>
+        <v>0.5812</v>
       </c>
       <c r="L5" t="n">
-        <v>4.61</v>
+        <v>1.94</v>
       </c>
       <c r="M5" t="n">
-        <v>47309</v>
+        <v>48359</v>
       </c>
       <c r="N5" t="n">
-        <v>459.49</v>
+        <v>466.7</v>
       </c>
     </row>
     <row r="6">
@@ -720,22 +720,22 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.539</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5404</v>
+        <v>0.5271</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5634</v>
+        <v>0.5558</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>119846</v>
+        <v>119910</v>
       </c>
       <c r="N6" t="n">
-        <v>408.3</v>
+        <v>420.46</v>
       </c>
     </row>
     <row r="7">
@@ -770,22 +770,22 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.66</v>
+        <v>0.517</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6201</v>
+        <v>0.5157</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6609</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4.66</v>
+        <v>2.51</v>
       </c>
       <c r="M7" t="n">
-        <v>950802</v>
+        <v>120038</v>
       </c>
       <c r="N7" t="n">
-        <v>503.75</v>
+        <v>432.82</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.641</v>
+        <v>0.507</v>
       </c>
       <c r="J8" t="n">
-        <v>0.613</v>
+        <v>0.5151</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6515</v>
+        <v>0.5429</v>
       </c>
       <c r="L8" t="n">
-        <v>11.13</v>
+        <v>5.09</v>
       </c>
       <c r="M8" t="n">
-        <v>237478</v>
+        <v>239430</v>
       </c>
       <c r="N8" t="n">
-        <v>634.77</v>
+        <v>662.52</v>
       </c>
     </row>
     <row r="9">
@@ -870,22 +870,22 @@
         <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.511</v>
+        <v>0.438</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5024</v>
+        <v>0.4258</v>
       </c>
       <c r="K9" t="n">
-        <v>0.519</v>
+        <v>0.4525</v>
       </c>
       <c r="L9" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>119846</v>
+        <v>120966</v>
       </c>
       <c r="N9" t="n">
-        <v>591.66</v>
+        <v>609.23</v>
       </c>
     </row>
     <row r="10">
@@ -920,22 +920,22 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.751</v>
+        <v>0.695</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7443</v>
+        <v>0.6883</v>
       </c>
       <c r="K10" t="n">
-        <v>0.751</v>
+        <v>0.6938</v>
       </c>
       <c r="L10" t="n">
-        <v>3.68</v>
+        <v>5.08</v>
       </c>
       <c r="M10" t="n">
-        <v>17251</v>
+        <v>17315</v>
       </c>
       <c r="N10" t="n">
-        <v>463.08</v>
+        <v>478.27</v>
       </c>
     </row>
     <row r="11">
@@ -970,22 +970,22 @@
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.75</v>
+        <v>0.715</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7457</v>
+        <v>0.7049</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7504</v>
+        <v>0.7153</v>
       </c>
       <c r="L11" t="n">
-        <v>17.26</v>
+        <v>8.52</v>
       </c>
       <c r="M11" t="n">
-        <v>130057</v>
+        <v>17443</v>
       </c>
       <c r="N11" t="n">
-        <v>1013.52</v>
+        <v>532.42</v>
       </c>
     </row>
     <row r="12">
@@ -1020,22 +1020,22 @@
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>0.742</v>
+        <v>0.679</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7338</v>
+        <v>0.6708</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7422</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>7.57</v>
+        <v>8.01</v>
       </c>
       <c r="M12" t="n">
-        <v>32291</v>
+        <v>34339</v>
       </c>
       <c r="N12" t="n">
-        <v>671.6900000000001</v>
+        <v>703.55</v>
       </c>
     </row>
     <row r="13">
@@ -1070,22 +1070,22 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.745</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7321</v>
+        <v>0.5578</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7451</v>
+        <v>0.5679</v>
       </c>
       <c r="L13" t="n">
-        <v>5.48</v>
+        <v>5.86</v>
       </c>
       <c r="M13" t="n">
-        <v>17251</v>
+        <v>18371</v>
       </c>
       <c r="N13" t="n">
-        <v>631.6900000000001</v>
+        <v>656.66</v>
       </c>
     </row>
   </sheetData>

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -670,22 +670,22 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.587</v>
+        <v>0.632</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5995</v>
+        <v>0.625</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5812</v>
+        <v>0.642</v>
       </c>
       <c r="L5" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="M5" t="n">
-        <v>48359</v>
+        <v>49415</v>
       </c>
       <c r="N5" t="n">
-        <v>466.7</v>
+        <v>470.29</v>
       </c>
     </row>
     <row r="6">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -670,22 +670,22 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.632</v>
+        <v>0.579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.625</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.642</v>
+        <v>0.5949</v>
       </c>
       <c r="L5" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
         <v>49415</v>
       </c>
       <c r="N5" t="n">
-        <v>470.29</v>
+        <v>470.16</v>
       </c>
     </row>
     <row r="6">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -529,13 +529,13 @@
         <v>0.6735</v>
       </c>
       <c r="L2" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="M2" t="n">
         <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>387.28</v>
+        <v>393.05</v>
       </c>
     </row>
     <row r="3">

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -520,22 +520,22 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.676</v>
+        <v>0.711</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6765</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6735</v>
+        <v>0.7107</v>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
       <c r="M2" t="n">
         <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>393.05</v>
+        <v>434.91</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.719</v>
+        <v>0.754</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7096</v>
+        <v>0.7517</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7215</v>
+        <v>0.7521</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>47431</v>
       </c>
       <c r="N3" t="n">
-        <v>399.02</v>
+        <v>444.84</v>
       </c>
     </row>
     <row r="4">
@@ -620,22 +620,22 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.729</v>
+        <v>0.744</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7188</v>
+        <v>0.7345</v>
       </c>
       <c r="K4" t="n">
-        <v>0.731</v>
+        <v>0.7461</v>
       </c>
       <c r="L4" t="n">
-        <v>1.84</v>
+        <v>2.47</v>
       </c>
       <c r="M4" t="n">
         <v>94183</v>
       </c>
       <c r="N4" t="n">
-        <v>482.79</v>
+        <v>488.47</v>
       </c>
     </row>
     <row r="5">
@@ -670,22 +670,22 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.579</v>
+        <v>0.617</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5949</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
         <v>49415</v>
       </c>
       <c r="N5" t="n">
-        <v>470.16</v>
+        <v>528.79</v>
       </c>
     </row>
     <row r="6">
@@ -720,22 +720,22 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.539</v>
+        <v>0.528</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5271</v>
+        <v>0.5148</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5558</v>
+        <v>0.5335</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>119910</v>
       </c>
       <c r="N6" t="n">
-        <v>420.46</v>
+        <v>467.62</v>
       </c>
     </row>
     <row r="7">
@@ -770,22 +770,22 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.517</v>
+        <v>0.62</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5157</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.6335</v>
       </c>
       <c r="L7" t="n">
-        <v>2.51</v>
+        <v>1.99</v>
       </c>
       <c r="M7" t="n">
         <v>120038</v>
       </c>
       <c r="N7" t="n">
-        <v>432.82</v>
+        <v>477.09</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.507</v>
+        <v>0.517</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5151</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5429</v>
+        <v>0.5436</v>
       </c>
       <c r="L8" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="M8" t="n">
         <v>239430</v>
       </c>
       <c r="N8" t="n">
-        <v>662.52</v>
+        <v>687.89</v>
       </c>
     </row>
     <row r="9">
@@ -870,22 +870,22 @@
         <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.438</v>
+        <v>0.428</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4258</v>
+        <v>0.4058</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4525</v>
+        <v>0.433</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6</v>
+        <v>5.13</v>
       </c>
       <c r="M9" t="n">
-        <v>120966</v>
+        <v>122022</v>
       </c>
       <c r="N9" t="n">
-        <v>609.23</v>
+        <v>733.09</v>
       </c>
     </row>
     <row r="10">
@@ -920,22 +920,22 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.695</v>
+        <v>0.662</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6883</v>
+        <v>0.6525</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6938</v>
+        <v>0.6672</v>
       </c>
       <c r="L10" t="n">
-        <v>5.08</v>
+        <v>6.36</v>
       </c>
       <c r="M10" t="n">
         <v>17315</v>
       </c>
       <c r="N10" t="n">
-        <v>478.27</v>
+        <v>509.21</v>
       </c>
     </row>
     <row r="11">
@@ -970,22 +970,22 @@
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.715</v>
+        <v>0.736</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7049</v>
+        <v>0.728</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7153</v>
+        <v>0.738</v>
       </c>
       <c r="L11" t="n">
-        <v>8.52</v>
+        <v>8.65</v>
       </c>
       <c r="M11" t="n">
         <v>17443</v>
       </c>
       <c r="N11" t="n">
-        <v>532.42</v>
+        <v>565.0700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1020,22 +1020,22 @@
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>0.679</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6708</v>
+        <v>0.6831</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6909</v>
       </c>
       <c r="L12" t="n">
-        <v>8.01</v>
+        <v>11.53</v>
       </c>
       <c r="M12" t="n">
         <v>34339</v>
       </c>
       <c r="N12" t="n">
-        <v>703.55</v>
+        <v>713.5700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1070,22 +1070,22 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5578</v>
+        <v>0.5739</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5679</v>
+        <v>0.5871</v>
       </c>
       <c r="L13" t="n">
-        <v>5.86</v>
+        <v>8.15</v>
       </c>
       <c r="M13" t="n">
-        <v>18371</v>
+        <v>19427</v>
       </c>
       <c r="N13" t="n">
-        <v>656.66</v>
+        <v>760.1799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/results/node_results.xlsx
+++ b/results/node_results.xlsx
@@ -529,13 +529,13 @@
         <v>0.7107</v>
       </c>
       <c r="L2" t="n">
-        <v>0.95</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
         <v>47303</v>
       </c>
       <c r="N2" t="n">
-        <v>434.91</v>
+        <v>429.02</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>0.7521</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="M3" t="n">
         <v>47431</v>
       </c>
       <c r="N3" t="n">
-        <v>444.84</v>
+        <v>438.56</v>
       </c>
     </row>
     <row r="4">
@@ -629,13 +629,13 @@
         <v>0.7461</v>
       </c>
       <c r="L4" t="n">
-        <v>2.47</v>
+        <v>3.02</v>
       </c>
       <c r="M4" t="n">
         <v>94183</v>
       </c>
       <c r="N4" t="n">
-        <v>488.47</v>
+        <v>514.36</v>
       </c>
     </row>
     <row r="5">
@@ -679,13 +679,13 @@
         <v>0.6133999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.85</v>
+        <v>3.57</v>
       </c>
       <c r="M5" t="n">
         <v>49415</v>
       </c>
       <c r="N5" t="n">
-        <v>528.79</v>
+        <v>523.99</v>
       </c>
     </row>
     <row r="6">
@@ -729,13 +729,13 @@
         <v>0.5335</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
         <v>119910</v>
       </c>
       <c r="N6" t="n">
-        <v>467.62</v>
+        <v>461.13</v>
       </c>
     </row>
     <row r="7">
